--- a/20251231_res_prem_exp.xlsx
+++ b/20251231_res_prem_exp.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lasallistasorg-my.sharepoint.com/personal/perez-jose_lasallistas_org_mx/Documents/Contabilidad y Auditoría de Seguros/Participación/Case 03/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Clases Facultad de Ciencias\Matemáticas Actuariales del Seguro de Personas II\masp2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="11_F25DC773A252ABDACC104804291E43925BDE58FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{955BE926-DB5C-46C0-A51F-68983E50480C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DE502C-68F7-4293-ADD7-A15626F26DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Total Reserves" sheetId="1" r:id="rId1"/>
@@ -5210,20 +5210,6 @@
   </cellStyles>
   <dxfs count="9">
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     </dxf>
     <dxf>
@@ -5247,6 +5233,20 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -5260,8 +5260,53 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>429280</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>160195</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C6DD519-E679-2D8C-18DA-9396226298EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5234940" y="914400"/>
+          <a:ext cx="4696480" cy="1257475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5269,7 +5314,7 @@
   <autoFilter ref="A6:B9" xr:uid="{153007F6-EFEB-41F9-8A63-7F90A1CD5D14}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{90C4DAFC-4D58-4889-B888-DE9015D25D44}" name="Product" totalsRowLabel="Total"/>
-    <tableColumn id="2" xr3:uid="{44A59DC2-1377-441B-BE14-6C82B5C51B11}" name="Reserve at 31DEC2025" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{44A59DC2-1377-441B-BE14-6C82B5C51B11}" name="Reserve at 31DEC2025" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5281,20 +5326,20 @@
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{AE2D25C2-D93A-4206-A112-2C90CDFFAEFD}" name="id_policy" totalsRowLabel="Total"/>
     <tableColumn id="2" xr3:uid="{0F8E9602-A8B5-43AE-8270-9AF4E995246E}" name="id_person"/>
-    <tableColumn id="3" xr3:uid="{03267E13-014D-4CC5-9881-76FEF72C0954}" name="pure_premium" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{DE7FDDE0-753C-4D9E-9ACE-6952B041B0FB}" name="gross_premium" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{95C82EB0-7CFA-4EB0-B9F1-57E6A1A6F939}" name="res_t" totalsRowFunction="sum" dataDxfId="2" totalsRowDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{03267E13-014D-4CC5-9881-76FEF72C0954}" name="pure_premium" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{DE7FDDE0-753C-4D9E-9ACE-6952B041B0FB}" name="gross_premium" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{95C82EB0-7CFA-4EB0-B9F1-57E6A1A6F939}" name="res_t" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{13652A76-EC06-42B4-B1AE-9245DF979DCD}" name="Table3" displayName="Table3" ref="A5:B94" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{13652A76-EC06-42B4-B1AE-9245DF979DCD}" name="Table3" displayName="Table3" ref="A5:B94" totalsRowShown="0" headerRowDxfId="8" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="A5:B94" xr:uid="{13652A76-EC06-42B4-B1AE-9245DF979DCD}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{390A713F-0C66-4380-90CE-9377815A4F2F}" name="age" dataDxfId="8" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{0781A80D-078A-4E2C-ABCA-D0B6D7B65D5C}" name="q_x" dataDxfId="7" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{390A713F-0C66-4380-90CE-9377815A4F2F}" name="age" dataDxfId="7" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{0781A80D-078A-4E2C-ABCA-D0B6D7B65D5C}" name="q_x" dataDxfId="6" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5632,8 +5677,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
